--- a/docs/DB/DbSpecifications.xlsx
+++ b/docs/DB/DbSpecifications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Program\C#\HouseholdAccountBook\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Program\C#\HouseholdAccountBook\docs\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078A0B3B-0A8B-4AE4-8E4D-AFD58F88E5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55A1CA2-3AF4-4F5B-A548-B64FF1EB1D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="869" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7710" yWindow="3090" windowWidth="21600" windowHeight="11295" tabRatio="869" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="備考(remark)" sheetId="4" r:id="rId10"/>
     <sheet name="Rel" sheetId="12" r:id="rId11"/>
     <sheet name="帳簿-項目(book_item)" sheetId="13" r:id="rId12"/>
+    <sheet name="Mtd" sheetId="14" r:id="rId13"/>
+    <sheet name="スキーマバージョン(schema_version)" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="219">
   <si>
     <t>テーブル論理名</t>
     <rPh sb="4" eb="7">
@@ -1155,6 +1157,33 @@
     </rPh>
     <rPh sb="31" eb="35">
       <t>ショウケンコウザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mtd_schema_version</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>version</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バージョン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メタデータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキーマバージョン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PostgreSQLのみ。1行のみ</t>
+    <rPh sb="14" eb="15">
+      <t>ギョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1244,7 +1273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1264,6 +1293,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1547,14 +1579,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D10"/>
+  <dimension ref="B2:E11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
-    <col min="2" max="3" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1564,8 +1598,11 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="E2" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
@@ -1576,7 +1613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
@@ -1587,7 +1624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B5" s="6" t="s">
         <v>188</v>
       </c>
@@ -1598,7 +1635,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
@@ -1609,7 +1646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
@@ -1620,7 +1657,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
@@ -1631,7 +1668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
@@ -1642,7 +1679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
@@ -1651,6 +1688,20 @@
       </c>
       <c r="D10" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B11" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1664,6 +1715,7 @@
     <hyperlink ref="B8" location="'分類(category)'!A1" display="mst_category" xr:uid="{00A03B14-0BD0-4A66-A7CE-342F682E6DB0}"/>
     <hyperlink ref="B9" location="'項目(item)'!A1" display="mst_item" xr:uid="{F48ABC00-5567-4F92-B80B-F0DBEC590B34}"/>
     <hyperlink ref="B10" location="'帳簿-項目(book_item)'!A1" display="rel_book_item" xr:uid="{B2D3E8FF-B862-4FAA-94EB-40D2A324AE47}"/>
+    <hyperlink ref="B11" location="'スキーマバージョン(schema_version)'!A1" display="mtd_schema_version" xr:uid="{47778E67-2115-4D13-8240-2CF2E5F64D9A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2011,6 +2063,79 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4DFFCE8-02CD-4056-9269-7F14B944DE7B}">
+  <sheetPr>
+    <tabColor theme="5" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD94830A-08C2-4E94-BBAC-7A3428F575EC}">
+  <dimension ref="B2:G4"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>

--- a/docs/DB/DbSpecifications.xlsx
+++ b/docs/DB/DbSpecifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Program\C#\HouseholdAccountBook\docs\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55A1CA2-3AF4-4F5B-A548-B64FF1EB1D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38A113B0-511D-4D15-9F55-6566497BD3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7710" yWindow="3090" windowWidth="21600" windowHeight="11295" tabRatio="869" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="869" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,19 @@
     <sheet name="帳簿(book)" sheetId="7" r:id="rId3"/>
     <sheet name="分類(category)" sheetId="8" r:id="rId4"/>
     <sheet name="項目(item)" sheetId="9" r:id="rId5"/>
-    <sheet name="Hst" sheetId="5" r:id="rId6"/>
-    <sheet name="帳簿項目(action)" sheetId="2" r:id="rId7"/>
-    <sheet name="グループ(group)" sheetId="3" r:id="rId8"/>
-    <sheet name="店舗(shop)" sheetId="11" r:id="rId9"/>
-    <sheet name="備考(remark)" sheetId="4" r:id="rId10"/>
-    <sheet name="Rel" sheetId="12" r:id="rId11"/>
-    <sheet name="帳簿-項目(book_item)" sheetId="13" r:id="rId12"/>
-    <sheet name="Mtd" sheetId="14" r:id="rId13"/>
-    <sheet name="スキーマバージョン(schema_version)" sheetId="15" r:id="rId14"/>
+    <sheet name="アセット(asset)" sheetId="16" r:id="rId6"/>
+    <sheet name="Hst" sheetId="5" r:id="rId7"/>
+    <sheet name="帳簿項目(action)" sheetId="2" r:id="rId8"/>
+    <sheet name="グループ(group)" sheetId="3" r:id="rId9"/>
+    <sheet name="店舗(shop)" sheetId="11" r:id="rId10"/>
+    <sheet name="備考(remark)" sheetId="4" r:id="rId11"/>
+    <sheet name="Rel" sheetId="12" r:id="rId12"/>
+    <sheet name="帳簿-項目(book_item)" sheetId="13" r:id="rId13"/>
+    <sheet name="Mtd" sheetId="14" r:id="rId14"/>
+    <sheet name="スキーマバージョン(schema_version)" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="222">
   <si>
     <t>テーブル論理名</t>
     <rPh sb="4" eb="7">
@@ -501,30 +503,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>item_name</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>category_id</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>advance_flg</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>updater</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>insert_time</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>inserter</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>項目ID</t>
     <rPh sb="0" eb="2">
       <t>コウモク</t>
@@ -532,81 +510,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>項目名</t>
-    <rPh sb="0" eb="3">
-      <t>コウモクメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カテゴリID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>○</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>PKEY</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>serial</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>text</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>integer</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>integer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>integer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>integer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>timestamp</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>text</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>立替フラグ</t>
-    <rPh sb="0" eb="2">
-      <t>タテカエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0：立替対象外
-1：立替対象</t>
-    <rPh sb="2" eb="4">
-      <t>タテカエ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ガイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>タテカエ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>タイショウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -895,26 +807,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>CBM_ITEM</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ITEM_ID</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ITEM_NAME</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CATEGORY_ID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SORT_KEY</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>CBT_ACT</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -968,38 +864,6 @@
   </si>
   <si>
     <t>balance_kind</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動フラグ</t>
-    <rPh sb="0" eb="2">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>move_flg</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>integer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0：移動以外
-1：移動用</t>
-    <rPh sb="2" eb="4">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ヨウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1185,6 +1049,191 @@
     <rPh sb="14" eb="15">
       <t>ギョウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>asset_id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アセットID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>asset_code</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>asset_name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>asset_kind</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アセット種別</t>
+    <rPh sb="4" eb="6">
+      <t>シュベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アセット名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アセットコード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>scale</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>prefix</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>suffix</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単位(前置)</t>
+    <rPh sb="0" eb="2">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マエオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単位(後置)</t>
+    <rPh sb="0" eb="2">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小数点以下桁数</t>
+    <rPh sb="0" eb="3">
+      <t>ショウスウテン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケタスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変換レート</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>◯</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>numeric/real</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0：通貨
+1：有価証券
+2：暗号資産
+3：ポイント
+4：その他</t>
+    <rPh sb="2" eb="4">
+      <t>ツウカ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ユウカショウケン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>アンゴウシサン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アセットマスタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mst_asset</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>v1以降</t>
+    <rPh sb="2" eb="4">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブ単位(前置)</t>
+    <rPh sb="2" eb="4">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>マエオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブ単位(後置)</t>
+    <rPh sb="2" eb="4">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sub_prefix</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sub_suffix</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブ単位名</t>
+    <rPh sb="2" eb="4">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>subunit_name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>base_rate</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1273,7 +1322,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1293,9 +1342,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1579,16 +1625,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E11"/>
+  <dimension ref="B2:F12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
     <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1598,11 +1644,14 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
@@ -1613,7 +1662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
@@ -1624,18 +1673,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B5" s="6" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.15">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
@@ -1646,7 +1695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
@@ -1657,7 +1706,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
@@ -1668,7 +1717,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
@@ -1679,29 +1728,43 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B10" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>16</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B11" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D11" t="s">
-        <v>216</v>
-      </c>
-      <c r="E11" t="s">
-        <v>218</v>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B12" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F12" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1714,8 +1777,9 @@
     <hyperlink ref="B7" location="'帳簿(book)'!A1" display="mst_book" xr:uid="{1681E9EB-039A-4AD5-B5A0-ECD10FC92965}"/>
     <hyperlink ref="B8" location="'分類(category)'!A1" display="mst_category" xr:uid="{00A03B14-0BD0-4A66-A7CE-342F682E6DB0}"/>
     <hyperlink ref="B9" location="'項目(item)'!A1" display="mst_item" xr:uid="{F48ABC00-5567-4F92-B80B-F0DBEC590B34}"/>
-    <hyperlink ref="B10" location="'帳簿-項目(book_item)'!A1" display="rel_book_item" xr:uid="{B2D3E8FF-B862-4FAA-94EB-40D2A324AE47}"/>
-    <hyperlink ref="B11" location="'スキーマバージョン(schema_version)'!A1" display="mtd_schema_version" xr:uid="{47778E67-2115-4D13-8240-2CF2E5F64D9A}"/>
+    <hyperlink ref="B11" location="'帳簿-項目(book_item)'!A1" display="rel_book_item" xr:uid="{B2D3E8FF-B862-4FAA-94EB-40D2A324AE47}"/>
+    <hyperlink ref="B12" location="'スキーマバージョン(schema_version)'!A1" display="mtd_schema_version" xr:uid="{47778E67-2115-4D13-8240-2CF2E5F64D9A}"/>
+    <hyperlink ref="B10" location="'アセット(asset)'!A1" display="mst_asset" xr:uid="{976DCA6C-5971-42E3-A25F-F1F02DA9AE8A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1723,8 +1787,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="B2:I12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="B2:H11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
@@ -1733,10 +1797,11 @@
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1753,141 +1818,121 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" t="s">
         <v>87</v>
       </c>
-      <c r="C3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D4" t="s">
-        <v>139</v>
-      </c>
       <c r="E4" t="s">
-        <v>145</v>
-      </c>
-      <c r="I4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="2:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>140</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1898,6 +1943,185 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="B2:J12"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="2.875" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
@@ -1913,9 +2137,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="B2:I10"/>
+  <dimension ref="B2:J10"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
@@ -1923,10 +2147,11 @@
     <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1943,29 +2168,32 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>59</v>
       </c>
-      <c r="I3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>80</v>
@@ -1976,65 +2204,65 @@
       <c r="E4" t="s">
         <v>59</v>
       </c>
-      <c r="I4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="2:10" ht="27" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
         <v>48</v>
       </c>
@@ -2042,18 +2270,18 @@
         <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
         <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2063,7 +2291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4DFFCE8-02CD-4056-9269-7F14B944DE7B}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
@@ -2079,16 +2307,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD94830A-08C2-4E94-BBAC-7A3428F575EC}">
-  <dimension ref="B2:G4"/>
+  <dimension ref="B2:H4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
+    <col min="1" max="1" width="2.875" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -2105,21 +2335,24 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>73</v>
       </c>
@@ -2154,7 +2387,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:I15"/>
+  <dimension ref="B2:J15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
@@ -2163,11 +2396,12 @@
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -2184,13 +2418,16 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
         <v>25</v>
       </c>
@@ -2203,11 +2440,11 @@
       <c r="E3" t="s">
         <v>59</v>
       </c>
-      <c r="I3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>40</v>
       </c>
@@ -2217,11 +2454,11 @@
       <c r="D4" t="s">
         <v>51</v>
       </c>
-      <c r="I4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>41</v>
       </c>
@@ -2231,11 +2468,11 @@
       <c r="D5" t="s">
         <v>52</v>
       </c>
-      <c r="I5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="J5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="67.5" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>42</v>
       </c>
@@ -2245,11 +2482,11 @@
       <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="H6" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
         <v>43</v>
       </c>
@@ -2262,41 +2499,41 @@
       <c r="F7" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="H7" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="F8" t="s">
-        <v>203</v>
-      </c>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+        <v>178</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
         <v>45</v>
       </c>
@@ -2306,14 +2543,14 @@
       <c r="D10" t="s">
         <v>54</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>61</v>
       </c>
-      <c r="I10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="27" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
         <v>44</v>
       </c>
@@ -2323,14 +2560,14 @@
       <c r="D11" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
         <v>47</v>
       </c>
@@ -2341,7 +2578,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
         <v>46</v>
       </c>
@@ -2352,7 +2589,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B14" t="s">
         <v>48</v>
       </c>
@@ -2363,7 +2600,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B15" t="s">
         <v>49</v>
       </c>
@@ -2383,7 +2620,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:I12"/>
+  <dimension ref="B2:J12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
@@ -2392,12 +2629,13 @@
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.125" customWidth="1"/>
-    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" customWidth="1"/>
+    <col min="10" max="10" width="16.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -2414,19 +2652,22 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="I2" s="5"/>
+      <c r="J2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
         <v>74</v>
@@ -2434,11 +2675,11 @@
       <c r="E3" t="s">
         <v>59</v>
       </c>
-      <c r="I3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>70</v>
       </c>
@@ -2448,44 +2689,44 @@
       <c r="D4" t="s">
         <v>75</v>
       </c>
-      <c r="I4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="27" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="I5" s="3"/>
+      <c r="J5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F6" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
         <v>45</v>
       </c>
@@ -2495,14 +2736,14 @@
       <c r="D7" t="s">
         <v>77</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>61</v>
       </c>
-      <c r="I7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="27" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
         <v>44</v>
       </c>
@@ -2512,15 +2753,15 @@
       <c r="D8" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="I8" s="3"/>
+      <c r="J8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
         <v>73</v>
       </c>
@@ -2531,7 +2772,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
         <v>46</v>
       </c>
@@ -2542,7 +2783,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
         <v>48</v>
       </c>
@@ -2553,7 +2794,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
         <v>49</v>
       </c>
@@ -2573,17 +2814,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:I14"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43B8848-F4A2-43B1-8B32-F7048B175D86}">
+  <dimension ref="B2:H20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
-    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -2600,175 +2852,235 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>87</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="67.5" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" t="s">
         <v>184</v>
       </c>
-      <c r="C7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" t="s">
-        <v>186</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D8" t="s">
-        <v>210</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B9" t="s">
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C15" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="D15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
         <v>61</v>
       </c>
-      <c r="I9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="B10" t="s">
+    </row>
+    <row r="16" spans="2:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B11" t="s">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B17" t="s">
         <v>73</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B12" t="s">
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B13" t="s">
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B14" t="s">
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B20" t="s">
         <v>49</v>
       </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2778,7 +3090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
@@ -2794,9 +3106,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:I17"/>
+  <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
@@ -2804,10 +3116,11 @@
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -2824,46 +3137,49 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>94</v>
+      </c>
+      <c r="J3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+        <v>95</v>
+      </c>
+      <c r="J4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
         <v>80</v>
@@ -2871,133 +3187,133 @@
       <c r="D5" t="s">
         <v>52</v>
       </c>
-      <c r="I5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" t="s">
-        <v>199</v>
-      </c>
       <c r="D8" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="27" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+        <v>177</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+        <v>82</v>
+      </c>
+      <c r="J10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="F11" t="s">
-        <v>127</v>
-      </c>
-      <c r="I11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
+        <v>110</v>
+      </c>
+      <c r="J11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="2:10" ht="27" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="J13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B14" t="s">
         <v>73</v>
       </c>
@@ -3008,7 +3324,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -3019,7 +3335,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B16" t="s">
         <v>48</v>
       </c>
@@ -3038,7 +3354,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3047,18 +3363,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B2:G11"/>
+  <dimension ref="B2:H11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -3075,15 +3392,18 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
@@ -3092,50 +3412,50 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="H4" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="F5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F6" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="2:8" ht="27" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
         <v>44</v>
       </c>
@@ -3143,24 +3463,24 @@
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
         <v>46</v>
       </c>
@@ -3168,10 +3488,10 @@
         <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
         <v>48</v>
       </c>
@@ -3182,7 +3502,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
         <v>49</v>
       </c>
@@ -3190,7 +3510,7 @@
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3198,156 +3518,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="2.875" customWidth="1"/>
-    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docs/DB/DbSpecifications.xlsx
+++ b/docs/DB/DbSpecifications.xlsx
@@ -1,36 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Program\C#\HouseholdAccountBook\docs\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38A113B0-511D-4D15-9F55-6566497BD3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13533416-A89B-4832-8D42-8FB83004BB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="869" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6645" yWindow="2580" windowWidth="21600" windowHeight="11295" tabRatio="869" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
-    <sheet name="Mst" sheetId="6" r:id="rId2"/>
-    <sheet name="帳簿(book)" sheetId="7" r:id="rId3"/>
-    <sheet name="分類(category)" sheetId="8" r:id="rId4"/>
-    <sheet name="項目(item)" sheetId="9" r:id="rId5"/>
-    <sheet name="アセット(asset)" sheetId="16" r:id="rId6"/>
-    <sheet name="Hst" sheetId="5" r:id="rId7"/>
-    <sheet name="帳簿項目(action)" sheetId="2" r:id="rId8"/>
-    <sheet name="グループ(group)" sheetId="3" r:id="rId9"/>
-    <sheet name="店舗(shop)" sheetId="11" r:id="rId10"/>
-    <sheet name="備考(remark)" sheetId="4" r:id="rId11"/>
-    <sheet name="Rel" sheetId="12" r:id="rId12"/>
-    <sheet name="帳簿-項目(book_item)" sheetId="13" r:id="rId13"/>
-    <sheet name="Mtd" sheetId="14" r:id="rId14"/>
-    <sheet name="スキーマバージョン(schema_version)" sheetId="15" r:id="rId15"/>
+    <sheet name="変更履歴" sheetId="18" r:id="rId2"/>
+    <sheet name="Mst" sheetId="6" r:id="rId3"/>
+    <sheet name="帳簿(book)" sheetId="7" r:id="rId4"/>
+    <sheet name="分類(category)" sheetId="8" r:id="rId5"/>
+    <sheet name="項目(item)" sheetId="17" r:id="rId6"/>
+    <sheet name="アセット(asset)" sheetId="16" r:id="rId7"/>
+    <sheet name="Hst" sheetId="5" r:id="rId8"/>
+    <sheet name="帳簿項目(action)" sheetId="2" r:id="rId9"/>
+    <sheet name="グループ(group)" sheetId="3" r:id="rId10"/>
+    <sheet name="店舗(shop)" sheetId="11" r:id="rId11"/>
+    <sheet name="備考(remark)" sheetId="4" r:id="rId12"/>
+    <sheet name="Rel" sheetId="12" r:id="rId13"/>
+    <sheet name="帳簿-項目(book_item)" sheetId="13" r:id="rId14"/>
+    <sheet name="Mtd" sheetId="14" r:id="rId15"/>
+    <sheet name="スキーマバージョン(schema_version)" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="248">
   <si>
     <t>テーブル論理名</t>
     <rPh sb="4" eb="7">
@@ -987,21 +987,6 @@
   </si>
   <si>
     <t>text</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0：移動
-1：繰返し
-2：リスト登録</t>
-    <rPh sb="2" eb="4">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>クリカエ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>トウロク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1236,11 +1221,237 @@
     <t>base_rate</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>CBM_ITEM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目名</t>
+    <rPh sb="0" eb="3">
+      <t>コウモクメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>item_name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ITEM_NAME</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立替フラグ</t>
+    <rPh sb="0" eb="2">
+      <t>タテカエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>advance_flg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0：立替対象外
+1：立替対象</t>
+    <rPh sb="2" eb="4">
+      <t>タテカエ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ガイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タテカエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動フラグ</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>move_flg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MOVE_FLG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>interger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分類ID</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0：移動
+1：繰返し
+2：リスト登録
+3：アセット変換</t>
+    <rPh sb="2" eb="4">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>クリカエ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>v2以降</t>
+    <rPh sb="2" eb="4">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>v3以降</t>
+    <rPh sb="2" eb="4">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mst_book.asset_id追加
+hst_action.asset_id追加</t>
+    <rPh sb="17" eb="19">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mst_asset追加</t>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mtd_schema_version追加</t>
+    <rPh sb="18" eb="20">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規作成</t>
+    <rPh sb="0" eb="2">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0：移動以外
+1：移動</t>
+    <rPh sb="2" eb="4">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分類種別</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>item_kind</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>v3以降
+0：通常・移動
+1：(欠番)
+2：変換</t>
+    <rPh sb="2" eb="4">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケツバン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mst_item.asset_id追加
+mst_item.item_kind追加</t>
+    <rPh sb="17" eb="19">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1322,7 +1533,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1342,6 +1553,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1645,7 +1862,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>39</v>
@@ -1730,16 +1947,16 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B10" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.15">
@@ -1755,16 +1972,16 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B12" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F12" t="s">
         <v>192</v>
-      </c>
-      <c r="D12" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1787,6 +2004,163 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="B2:H11"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="2.875" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="54" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="2:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B2:H11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -1818,7 +2192,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>39</v>
@@ -1942,7 +2316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:J12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -1974,7 +2348,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>39</v>
@@ -2121,7 +2495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
@@ -2137,7 +2511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B2:J10"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -2168,7 +2542,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>39</v>
@@ -2291,7 +2665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4DFFCE8-02CD-4056-9269-7F14B944DE7B}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
@@ -2307,7 +2681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD94830A-08C2-4E94-BBAC-7A3428F575EC}">
   <dimension ref="B2:H4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -2335,7 +2709,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>39</v>
@@ -2343,10 +2717,10 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
         <v>52</v>
@@ -2370,6 +2744,87 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AD71E9-79DF-4BAE-993F-6BAA39FA60C2}">
+  <dimension ref="B2:D7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="8">
+        <v>46053</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5" s="8">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="8">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D7" s="8">
+        <v>46250</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
@@ -2385,9 +2840,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:J15"/>
+  <dimension ref="B2:J16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
@@ -2418,7 +2873,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>39</v>
@@ -2460,154 +2915,171 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="67.5" x14ac:dyDescent="0.15">
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="J6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="67.5" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>179</v>
+        <v>52</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>54</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" t="s">
         <v>61</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J11" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="B11" t="s">
+    <row r="12" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B12" t="s">
         <v>44</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J12" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B16" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2618,7 +3090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:J12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -2652,7 +3124,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>39</v>
@@ -2812,17 +3284,248 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC582330-C0F8-4284-BAD4-F0AAE04E542B}">
+  <dimension ref="B2:I16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="2.875" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="54" x14ac:dyDescent="0.15">
+      <c r="B5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="B8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="B9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43B8848-F4A2-43B1-8B32-F7048B175D86}">
   <dimension ref="B2:H20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -2852,7 +3555,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>39</v>
@@ -2860,10 +3563,10 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
@@ -2874,10 +3577,10 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -2885,10 +3588,10 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" t="s">
         <v>219</v>
-      </c>
-      <c r="C5" t="s">
-        <v>220</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -2899,38 +3602,38 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="67.5" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D8" t="s">
         <v>52</v>
@@ -2938,10 +3641,10 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D9" t="s">
         <v>51</v>
@@ -2949,10 +3652,10 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -2960,10 +3663,10 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D11" t="s">
         <v>51</v>
@@ -2974,10 +3677,10 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D12" t="s">
         <v>51</v>
@@ -2988,13 +3691,13 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.15">
@@ -3090,7 +3793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
@@ -3106,9 +3809,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:J17"/>
+  <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.875" customWidth="1"/>
@@ -3137,7 +3840,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>39</v>
@@ -3165,195 +3868,212 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J4" t="s">
-        <v>152</v>
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>208</v>
+      </c>
+      <c r="H4" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="J5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B9" t="s">
         <v>167</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>174</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>166</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="B9" t="s">
+    <row r="10" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
         <v>181</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>180</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>177</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" t="s">
-        <v>82</v>
-      </c>
-      <c r="J10" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" t="s">
+        <v>110</v>
+      </c>
+      <c r="J12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B13" t="s">
         <v>183</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>184</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>185</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="2:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="B13" t="s">
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B14" t="s">
         <v>44</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>100</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>52</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J14" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B15" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B18" t="s">
         <v>49</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>36</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3361,161 +4081,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B2:H11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="2.875" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="2:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
 </file>